--- a/ProjectDescription/SettingsFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/SettingsFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1024,6 +1024,234 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SettingsFragment</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>设置Fragment，提供下载路径、合并开关、画质选择等配置</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment:22]</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，设置Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化设置项控件</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;onCreateView:32]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>后续实现SharedPreferences持久化存储</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SettingsFragment</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>设置Fragment，提供下载路径、合并开关、画质选择等配置</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment:22]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，设置Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化设置项控件</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;onCreateView:32]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>后续实现SharedPreferences持久化存储</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SettingsFragment</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>设置Fragment，提供下载路径、合并开关、画质选择等配置</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment:22]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，设置Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化设置项控件</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;onCreateView:32]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>后续实现SharedPreferences持久化存储</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/SettingsFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/SettingsFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1252,6 +1252,82 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SettingsFragment</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>设置Fragment，提供下载路径、合并开关、画质选择等配置</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment:22]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，设置Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化设置项控件</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;onCreateView:32]</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>后续实现SharedPreferences持久化存储</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/SettingsFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/SettingsFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1328,6 +1328,166 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>checkForUpdate</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>检查更新的入口方法，调用UpdateManager异步检查GitHub Releases</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;checkForUpdate:139]</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月21日00时45分09秒</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>按钮文字变为检查中...，完成后恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>resetCheckUpdateButton</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>恢复检查更新按钮的初始状态</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;resetCheckUpdateButton:183]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月21日00时45分09秒</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>恢复文字为检查，启用点击</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>showUpdateDialog</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>versionName&lt;String&gt;, releaseNotes&lt;String&gt;, apkUrl&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>显示发现新版本的对话框</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;showUpdateDialog:194]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月21日00时45分09秒</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>点击立即更新触发startDownload</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>startDownload</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>apkUrl&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>开始下载APK并显示进度对话框</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/settings/SettingsFragment.java)[SettingsFragment-&gt;startDownload:214]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月21日00时45分09秒</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>含水平进度条，下载完成自动安装</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
